--- a/templates/TAB시가소개 발송용.xlsx
+++ b/templates/TAB시가소개 발송용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DAILYCIGAR_DB\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33EA8EEF-1570-4DDC-A441-DA4910F32C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED43E33E-0A22-421A-AD76-5B923AFFE5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1CC1957B-9493-4AEF-97AC-BA69A6C490DF}"/>
   </bookViews>
@@ -150,7 +150,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -160,6 +160,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -193,7 +199,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -211,6 +217,9 @@
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -563,37 +572,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="6" t="s">
         <v>17</v>
       </c>
     </row>

--- a/templates/TAB시가소개 발송용.xlsx
+++ b/templates/TAB시가소개 발송용.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DAILYCIGAR_DB\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED43E33E-0A22-421A-AD76-5B923AFFE5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA04632-CB6A-41D0-99DD-D637361E7D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1CC1957B-9493-4AEF-97AC-BA69A6C490DF}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="상품소개서" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
